--- a/光伏配储项目/电价数据/2026/乐桥站.xlsx
+++ b/光伏配储项目/电价数据/2026/乐桥站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33793</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.77115</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07678</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.97854</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.02087</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17455</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27213</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25582</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24511</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.8329</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6099199999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.59151</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7637699999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14858</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43577</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44286</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.67583</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5531200000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.23013</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.44692</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.07805</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.08628</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.33019</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.39227</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.46389</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.72421</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.77955</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.31094</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.8108500000000001</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.85254</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79073</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.73441</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.49213</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4568</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.45295</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.41417</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70924</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.616</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.88971</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8577400000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48502</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.49904</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49164</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49207</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47564</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.45862</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49284</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.5279299999999999</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.53006</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.67675</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6382000000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.89752</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.11313</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.75059</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5366799999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.44303</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.41581</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.71168</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38434</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.21842</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.67167</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.99918</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.20524</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.41772</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.24033</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.01733</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.39822</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.2221</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.44496</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.06633</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.20673</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.87666</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.11357</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.03123</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05564</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9141</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.16621</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.99013</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.47413</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.9147000000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91354</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.47176</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.44696</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.46545</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33412</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51103</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48986</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42121</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43564</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39072</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46373</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.43955</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43158</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19524</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27773</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.11589</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.9055700000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.73154</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.71873</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.94704</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.9437300000000001</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.9720700000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.9410599999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.81464</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.81902</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.83065</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.05435</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.58526</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.65487</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.94725</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.92055</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.7467</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8168200000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.55561</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.01069</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.55925</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.41866</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45763</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5381699999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.6904400000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.74182</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6955</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6716599999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.66862</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7011799999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.49442</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5239199999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.66503</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.87505</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.80062</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.15371</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48004</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.66184</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.48636</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.6189</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.78025</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.97312</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.66539</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.16696</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.83972</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.6390800000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5749500000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71423</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.47776</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34162</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.50012</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.48093</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43045</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44808</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44167</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5283300000000001</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.78291</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47599</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46306</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.75081</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.46096</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.78788</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.62548</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.49097</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.60393</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.39747</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.70243</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.01241</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.70043</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.6653300000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.53238</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.5667000000000001</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.6668500000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.84099</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.59396</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6620499999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.63298</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.6051</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5025500000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.48189</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.47023</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.37858</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14326</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02351</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40869</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.45547</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25779</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24197</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10718</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.28874</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03286</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.43789</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42276</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3165</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29818</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23649</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24346</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.25748</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28629</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18848</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.18162</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24649</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.19328</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24649</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21232</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18995</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17099</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24725</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26889</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19822</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26608</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09609999999999999</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03949</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00991</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20601</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04917</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27513</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19421</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.008670000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06016</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05836</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31535</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.43094</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.44436</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48365</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7879700000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87029</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65211</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5715800000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44463</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41768</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44352</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.46145</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58243</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6305700000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.94167</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.5552</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43663</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44258</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.74393</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.98284</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26513</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.41834</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.75788</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6028600000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17654</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27585</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26018</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28011</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3229</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.82823</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.53199</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.61161</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45874</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.4931</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.22908</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.53626</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.6181</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.48214</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.46867</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.45923</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.47579</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.62625</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.49714</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.46199</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.49733</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.49795</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.49827</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.33778</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.27362</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.43823</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.74637</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.96793</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.83817</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.9168500000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.51851</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5625599999999999</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.44415</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45944</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39789</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.56247</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.23669</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46811</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16869</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.008840000000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.44244</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.51209</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30154</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30705</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.19424</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.21006</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18415</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.20481</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18141</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.17287</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26502</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.23986</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.23377</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18299</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.28249</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26994</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.20369</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.17933</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.21753</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.22004</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.24625</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28839</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28437</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26832</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27261</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.29818</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27952</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27955</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24709</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27983</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28837</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26077</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28714</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28758</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4411600000000001</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30276</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.07376</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41577</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.65852</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.48871</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48726</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43701</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.49642</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42953</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5518200000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27666</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.44057</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.43507</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.76228</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.5641799999999999</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43644</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41513</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.53967</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.45825</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.45543</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.51271</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.58924</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.8676</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47997</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.56731</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.5603400000000001</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.8005</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50497</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.44239</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.26608</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28874</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19518</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18757</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.2761</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27551</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27306</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27593</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27604</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27277</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18934</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18672</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.14968</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23321</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26069</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18645</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19219</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.19876</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16243</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.15401</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.23049</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.24768</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40197</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26159</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.40774</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.25846</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28532</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27172</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28687</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.24512</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.22341</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23166</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31991</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.02546</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28762</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27214</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28164</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.2820299999999999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.2728</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27262</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26952</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.5934700000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.51835</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.2005</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29556</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40959</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44148</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49447</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6230399999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5848</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.63079</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7757000000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4831</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31315</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.27801</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44784</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40245</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42053</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44396</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47659</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5159400000000001</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57436</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43305</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.70838</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8171</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48922</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.43198</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.41215</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.69287</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5628500000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6418200000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31229</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26169</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.01173</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27335</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27309</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.46977</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.47809</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.4782</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.5650700000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41638</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44441</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.44452</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.43745</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.46666</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.23918</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26605</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25646</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.30328</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.21562</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.24668</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.22582</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16214</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.01328</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.26706</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.01521</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.16238</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.02709</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19629</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.16117</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.01551</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15642</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19223</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15412</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15677</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.01589</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16207</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.01599</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.04176</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17271</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17836</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.14465</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.04871</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.16088</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.2056</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.50956</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00053</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21547</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.26486</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.21172</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.26501</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.19821</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.21377</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.29997</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22641</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.28782</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27122</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.03349</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18093</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.17802</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26445</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.02746</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19751</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21912</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21056</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.01948</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.0252</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.02521</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.02548</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.02548</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.02532</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19211</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.03972</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.02548</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.02547</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17011</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.02461</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.02147</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24328</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.01794</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00831</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.22508</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00532</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.02017</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02562</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.04111</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03064</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.02465</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26589</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.00923</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.2724</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27742</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27474</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.16148</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.15683</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16108</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15474</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.02135</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.02022</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.01833</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41365</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18465</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27303</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.22899</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.28517</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85661</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8624299999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08929999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24567</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00259</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00184</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06936</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47539</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.6254299999999999</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50413</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.74441</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.89003</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.57947</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.78396</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.75962</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.75785</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.7615299999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.84794</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30487</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.45273</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.2643</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25878</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.18254</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25525</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24963</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24318</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.20985</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.24732</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19603</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.19172</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.15679</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.14843</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17375</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.27253</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23489</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24375</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.2492</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27288</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25867</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28768</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28863</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5524</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45171</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4594</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.18368</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7644500000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.77016</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.41875</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.52025</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6472599999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.80541</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.54389</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42301</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19873</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31432</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49343</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.50298</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.01076</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.77347</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.53438</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.67901</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46467</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5508500000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49924</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6541399999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.6139199999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.95329</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7761</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.67418</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.56363</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31894</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28285</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28116</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28713</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.2780899999999999</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26477</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42531</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5432899999999999</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19845</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.51148</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.47974</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.5063799999999999</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.66534</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.65712</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.6899500000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.54249</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.43104</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44732</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.53618</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.46074</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32276</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.67143</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.44136</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27379</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.45667</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.80932</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.83924</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.55887</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.67814</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.90211</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.41773</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.57297</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.6114299999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.42534</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4977200000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41591</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40598</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33685</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.44324</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17612</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14578</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19869</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14675</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12183</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22637</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26016</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14334</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.1456</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18751</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22688</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.18939</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.20243</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.22889</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.2036</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.43961</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.43902</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.44258</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.7763300000000001</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.88405</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.59441</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.49697</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.65398</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.47992</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.46117</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.52447</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.43273</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.8064</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.6764600000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.8479</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.27057</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.8982100000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.45265</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.81678</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.45484</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.7767200000000001</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.81211</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.65749</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.46767</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36708</v>
       </c>
     </row>
   </sheetData>
